--- a/artfynd/A 35525-2025 artfynd.xlsx
+++ b/artfynd/A 35525-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126560148</v>
+        <v>126560149</v>
       </c>
       <c r="B2" t="n">
-        <v>95604</v>
+        <v>95768</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2810</v>
+        <v>2667</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>437220</v>
+        <v>437274</v>
       </c>
       <c r="R2" t="n">
-        <v>6227758</v>
+        <v>6227775</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126560149</v>
+        <v>126560148</v>
       </c>
       <c r="B3" t="n">
-        <v>95693</v>
+        <v>95679</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2667</v>
+        <v>2810</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>437274</v>
+        <v>437220</v>
       </c>
       <c r="R3" t="n">
-        <v>6227775</v>
+        <v>6227758</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>

--- a/artfynd/A 35525-2025 artfynd.xlsx
+++ b/artfynd/A 35525-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126560149</v>
       </c>
       <c r="B2" t="n">
-        <v>95768</v>
+        <v>95774</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>126560148</v>
       </c>
       <c r="B3" t="n">
-        <v>95679</v>
+        <v>95685</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35525-2025 artfynd.xlsx
+++ b/artfynd/A 35525-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126560149</v>
       </c>
       <c r="B2" t="n">
-        <v>95774</v>
+        <v>95768</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>126560148</v>
       </c>
       <c r="B3" t="n">
-        <v>95685</v>
+        <v>95679</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35525-2025 artfynd.xlsx
+++ b/artfynd/A 35525-2025 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>131116964</v>
       </c>
       <c r="B4" t="n">
-        <v>56762</v>
+        <v>56764</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>131117036</v>
       </c>
       <c r="B5" t="n">
-        <v>56748</v>
+        <v>56750</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>131116934</v>
       </c>
       <c r="B6" t="n">
-        <v>56769</v>
+        <v>56771</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>131117021</v>
       </c>
       <c r="B7" t="n">
-        <v>56746</v>
+        <v>56748</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 35525-2025 artfynd.xlsx
+++ b/artfynd/A 35525-2025 artfynd.xlsx
@@ -879,37 +879,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131116964</v>
+        <v>131117036</v>
       </c>
       <c r="B4" t="n">
-        <v>56764</v>
+        <v>56751</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>443</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -994,37 +994,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131117036</v>
+        <v>131116964</v>
       </c>
       <c r="B5" t="n">
-        <v>56750</v>
+        <v>56765</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>443</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -1112,7 +1112,7 @@
         <v>131116934</v>
       </c>
       <c r="B6" t="n">
-        <v>56771</v>
+        <v>56772</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>131117021</v>
       </c>
       <c r="B7" t="n">
-        <v>56748</v>
+        <v>56749</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 35525-2025 artfynd.xlsx
+++ b/artfynd/A 35525-2025 artfynd.xlsx
@@ -879,37 +879,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131117036</v>
+        <v>131116964</v>
       </c>
       <c r="B4" t="n">
-        <v>56751</v>
+        <v>56765</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>443</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -994,37 +994,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131116964</v>
+        <v>131117036</v>
       </c>
       <c r="B5" t="n">
-        <v>56765</v>
+        <v>56751</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>443</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>

--- a/artfynd/A 35525-2025 artfynd.xlsx
+++ b/artfynd/A 35525-2025 artfynd.xlsx
@@ -1227,7 +1227,7 @@
         <v>131117021</v>
       </c>
       <c r="B7" t="n">
-        <v>56754</v>
+        <v>56760</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 35525-2025 artfynd.xlsx
+++ b/artfynd/A 35525-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126560149</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126560147</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126560148</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1093,6 +1113,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131117021</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1208,6 +1233,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131116963</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1323,6 +1353,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131117035</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1438,8 +1473,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131116934</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>